--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261007.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261007.xlsx
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.7074742268041238</v>
+        <v>0.7085051546391753</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.1492061855670102</v>
+        <v>0.1502371134020618</v>
       </c>
     </row>
     <row r="8">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>11-1</t>
+          <t>11-2</t>
         </is>
       </c>
       <c r="C72" s="19" t="inlineStr">
         <is>
-          <t>一次資料との全件突合</t>
+          <t>図表データ管理台帳の整備と運用</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
@@ -7974,7 +7974,7 @@
         <v>65</v>
       </c>
       <c r="K72" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L72" s="33" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="M72" s="19" t="inlineStr">
         <is>
-          <t>**町データが届くたびに突合対象が増える。とくに成果指標の現状値17項目と令和7年度決算が入ると、素案・算定シート・協議会資料の3系統を同時に照合する必要がある**</t>
+          <t>**足りない図6件のうち、10月4日に要介護度の維持・改善を作成し、残りは2件になった。****いずれも町データ待ちである。**地域ケア会議の開催回数・検討件数（町の事業実績待ち）と、介護給付適正化の主要3事業の実施状況（町の実施報告待ち）</t>
         </is>
       </c>
     </row>
@@ -7995,12 +7995,12 @@
       </c>
       <c r="B73" s="20" t="inlineStr">
         <is>
-          <t>11-2</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C73" s="19" t="inlineStr">
         <is>
-          <t>図表データ管理台帳の整備と運用</t>
+          <t>ペンディング項目の整理と作業順位の管理</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
@@ -8010,12 +8010,12 @@
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -8024,16 +8024,16 @@
         </is>
       </c>
       <c r="H73" s="32" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="I73" s="32" t="n">
-        <v>20</v>
+        <v>3.3</v>
       </c>
       <c r="J73" s="32" t="n">
-        <v>65</v>
+        <v>66.7</v>
       </c>
       <c r="K73" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L73" s="33" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="M73" s="19" t="inlineStr">
         <is>
-          <t>**足りない図6件のうち、10月4日に要介護度の維持・改善を作成し、残りは2件になった。****いずれも町データ待ちである。**地域ケア会議の開催回数・検討件数（町の事業実績待ち）と、介護給付適正化の主要3事業の実施状況（町の実施報告待ち）</t>
+          <t>**町の回答が届くたびに順位を組み替える。優先1位（基金運用状況調書）の回答が来た時点で、その日の作業を止めて差し替えに回す**</t>
         </is>
       </c>
     </row>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>11-1</t>
         </is>
       </c>
       <c r="C74" s="19" t="inlineStr">
         <is>
-          <t>ペンディング項目の整理と作業順位の管理</t>
+          <t>一次資料との全件突合</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F74" s="20" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G74" s="23" t="inlineStr">
@@ -8083,16 +8083,16 @@
         </is>
       </c>
       <c r="H74" s="32" t="n">
+        <v>90</v>
+      </c>
+      <c r="I74" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="J74" s="32" t="n">
         <v>70</v>
       </c>
-      <c r="I74" s="32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J74" s="32" t="n">
-        <v>66.7</v>
-      </c>
       <c r="K74" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L74" s="33" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="M74" s="19" t="inlineStr">
         <is>
-          <t>**町の回答が届くたびに順位を組み替える。優先1位（基金運用状況調書）の回答が来た時点で、その日の作業を止めて差し替えに回す**</t>
+          <t>**町データが届くたびに突合対象が増える。とくに成果指標の現状値17項目と令和7年度決算が入ると、素案・算定シート・協議会資料の3系統を同時に照合する必要がある**</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
     <row r="80">
       <c r="A80" s="34" t="inlineStr">
         <is>
-          <t>加重の実績進捗率 70.7％　対　予定進捗率 55.8％　乖離 +14.9ポイント</t>
+          <t>加重の実績進捗率 70.9％　対　予定進捗率 55.8％　乖離 +15.0ポイント</t>
         </is>
       </c>
     </row>
@@ -14370,14 +14370,14 @@
         </is>
       </c>
       <c r="L73" s="22" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M73" s="23" t="n">
         <v>4</v>
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>**check_ono_ichiji.py が286件を毎回照合し、NGがあれば止まる。現在NGは0件である。****9月29日に調査結果報告書の原本を取り込み、配布・回収、リスク該当率10項目、通いの場、外出、認知症（問35・問36）、在宅介護実態調査の属性・利用状況・未利用理由・介護者、問9（仕事と介護の両立の支援12項目）を全件突合した。****これにより、報告書そのものの食い違い3件を特定した**（①回収数319に対し集計基数366、②通いの場が本文67.2％・図76.2％、③p.84のまとめで項目名が重複）。**あわせて、当方の成果品にあった項目名の取り違えを正した。**問36の54.1％は「相談窓口の充実」ではなく**「地域での見守りや声掛け」**であり、選択肢に「相談窓口の充実」は存在しない（素案・協議会資料・調査結果の分析・交付金の4点を訂正）。**点検の結果はOK 280件・NG 0件・説明のつく相違4件・一次資料が手元にないもの2件である。**相違はいずれも理由とともに記録している</t>
+          <t>**check_ono_ichiji.py が329件を毎回照合し、NGがあれば止まる。現在NGは0件である。****令和8年10月8日に国保連月報からの突合43件を追加した。**それまで月報からの突合は0件で、「961人から862人へ99人減」「給付件数1,303件から1,365件へ」「前年同期比0.9598」といった月報由来の数値が16本のビルダーに手で書かれたまま、月報が1か月増えても誰も気づかない状態だった。**追加した突合で、帳票の構造の読み違いも1件捕まえた**（居宅介護支援と介護予防支援は「居宅サービス計」の外にあり、合計＝3区分計＋総合事業計＋居宅介護支援＋介護予防支援である）。**9月29日に調査結果報告書の原本を取り込み、配布・回収、リスク該当率10項目、通いの場、外出、認知症（問35・問36）、在宅介護実態調査の属性・利用状況・未利用理由・介護者、問9（仕事と介護の両立の支援12項目）を全件突合した。****これにより、報告書そのものの食い違い3件を特定した**（①回収数319に対し集計基数366、②通いの場が本文67.2％・図76.2％、③p.84のまとめで項目名が重複）。**あわせて、当方の成果品にあった項目名の取り違えを正した。**問36の54.1％は「相談窓口の充実」ではなく**「地域での見守りや声掛け」**であり、選択肢に「相談窓口の充実」は存在しない（素案・協議会資料・調査結果の分析・交付金の4点を訂正）。**点検の結果はOK 280件・NG 0件・説明のつく相違4件・一次資料が手元にないもの2件である。**相違はいずれも理由とともに記録している</t>
         </is>
       </c>
       <c r="O73" s="19" t="inlineStr">
